--- a/pensum/ol18/OL18_Personalpolitikk_og_rekruttering_Regneark_Hva_en_feilansettelse_koster.xlsx
+++ b/pensum/ol18/OL18_Personalpolitikk_og_rekruttering_Regneark_Hva_en_feilansettelse_koster.xlsx
@@ -1133,7 +1133,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1300,6 +1300,10 @@
     </xf>
     <xf numFmtId="171" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1612,7 +1616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -1634,7 +1638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -2090,8 +2094,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="21" t="s">
+    <row ht="27" customHeight="true" r="45" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A45" t="s">
         <v>90</v>
       </c>
       <c r="B45" s="23" t="s">
@@ -2112,8 +2116,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="21" t="s">
+    <row ht="27" customHeight="true" r="47" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A47" t="s">
         <v>94</v>
       </c>
       <c r="B47" s="23" t="s">
@@ -2123,8 +2127,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="21" t="s">
+    <row ht="27" customHeight="true" r="48" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A48" t="s">
         <v>95</v>
       </c>
       <c r="B48" s="23" t="s">
@@ -2145,8 +2149,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="21" t="s">
+    <row ht="27" customHeight="true" r="50" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A50" t="s">
         <v>98</v>
       </c>
       <c r="B50" s="23" t="s">
@@ -2156,8 +2160,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="21" t="s">
+    <row ht="27" customHeight="true" r="51" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A51" t="s">
         <v>101</v>
       </c>
       <c r="B51" s="23" t="s">
@@ -2247,8 +2251,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+    <row ht="27" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A5" t="s">
         <v>115</v>
       </c>
       <c r="B5" s="25" t="n">
